--- a/data/nzd0336/nzd0336.xlsx
+++ b/data/nzd0336/nzd0336.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K450"/>
+  <dimension ref="A1:K451"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17980,6 +17980,45 @@
         <v>325.82</v>
       </c>
       <c r="K450" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:19:36+00:00</t>
+        </is>
+      </c>
+      <c r="B451" t="n">
+        <v>388.18</v>
+      </c>
+      <c r="C451" t="n">
+        <v>373.58</v>
+      </c>
+      <c r="D451" t="n">
+        <v>369.87</v>
+      </c>
+      <c r="E451" t="n">
+        <v>360.54</v>
+      </c>
+      <c r="F451" t="n">
+        <v>347.43</v>
+      </c>
+      <c r="G451" t="n">
+        <v>340.66</v>
+      </c>
+      <c r="H451" t="n">
+        <v>332.34</v>
+      </c>
+      <c r="I451" t="n">
+        <v>330.57</v>
+      </c>
+      <c r="J451" t="n">
+        <v>327.92</v>
+      </c>
+      <c r="K451" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -17996,7 +18035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B521"/>
+  <dimension ref="A1:B522"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23209,6 +23248,16 @@
       </c>
       <c r="B521" t="n">
         <v>-0.98</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B522" t="n">
+        <v>-0.1</v>
       </c>
     </row>
   </sheetData>
@@ -23377,28 +23426,28 @@
         <v>0.0861</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2929828171358636</v>
+        <v>0.2978878384351051</v>
       </c>
       <c r="J2" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="K2" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05277887291447003</v>
+        <v>0.05452084257806145</v>
       </c>
       <c r="M2" t="n">
-        <v>7.100528176060472</v>
+        <v>7.109372733900052</v>
       </c>
       <c r="N2" t="n">
-        <v>89.51477780341474</v>
+        <v>89.62346784354854</v>
       </c>
       <c r="O2" t="n">
-        <v>9.461224963154335</v>
+        <v>9.466967193539256</v>
       </c>
       <c r="P2" t="n">
-        <v>368.6517709892212</v>
+        <v>368.6020673778048</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -23455,28 +23504,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3931376254950327</v>
+        <v>0.3948673421648608</v>
       </c>
       <c r="J3" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="K3" t="n">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1025944686665404</v>
+        <v>0.1037859411013426</v>
       </c>
       <c r="M3" t="n">
-        <v>6.795261031363048</v>
+        <v>6.788478114333539</v>
       </c>
       <c r="N3" t="n">
-        <v>77.05646519125507</v>
+        <v>76.92132241927973</v>
       </c>
       <c r="O3" t="n">
-        <v>8.778181200639178</v>
+        <v>8.770480170394306</v>
       </c>
       <c r="P3" t="n">
-        <v>359.1161811051306</v>
+        <v>359.0983883857173</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23533,28 +23582,28 @@
         <v>0.1199</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2326063546900652</v>
+        <v>0.2314087223911647</v>
       </c>
       <c r="J4" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="K4" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03059435173387082</v>
+        <v>0.03041878408977117</v>
       </c>
       <c r="M4" t="n">
-        <v>6.239840919422612</v>
+        <v>6.230385719040849</v>
       </c>
       <c r="N4" t="n">
-        <v>98.22280364423349</v>
+        <v>98.02153385108873</v>
       </c>
       <c r="O4" t="n">
-        <v>9.910741831176589</v>
+        <v>9.900582500595039</v>
       </c>
       <c r="P4" t="n">
-        <v>366.580485572791</v>
+        <v>366.5927532763199</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -23611,28 +23660,28 @@
         <v>0.0964</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1277986706366946</v>
+        <v>0.127909154367618</v>
       </c>
       <c r="J5" t="n">
+        <v>450</v>
+      </c>
+      <c r="K5" t="n">
         <v>449</v>
       </c>
-      <c r="K5" t="n">
-        <v>448</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.0157268248702328</v>
+        <v>0.01582410712398985</v>
       </c>
       <c r="M5" t="n">
-        <v>5.750051053226599</v>
+        <v>5.737885897212609</v>
       </c>
       <c r="N5" t="n">
-        <v>59.47015327184176</v>
+        <v>59.33785947888155</v>
       </c>
       <c r="O5" t="n">
-        <v>7.711689391556286</v>
+        <v>7.703107131468545</v>
       </c>
       <c r="P5" t="n">
-        <v>356.900819723041</v>
+        <v>356.8997002881936</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -23689,28 +23738,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5782639179593877</v>
+        <v>0.5761392938484973</v>
       </c>
       <c r="J6" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="K6" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3346129539176202</v>
+        <v>0.3336533733192707</v>
       </c>
       <c r="M6" t="n">
-        <v>4.821228874672332</v>
+        <v>4.821430461271814</v>
       </c>
       <c r="N6" t="n">
-        <v>38.63696041632652</v>
+        <v>38.60881506080794</v>
       </c>
       <c r="O6" t="n">
-        <v>6.215863609855554</v>
+        <v>6.213599203425334</v>
       </c>
       <c r="P6" t="n">
-        <v>337.2925838385112</v>
+        <v>337.3141131010304</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23767,28 +23816,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4730689499266164</v>
+        <v>0.4692730758454123</v>
       </c>
       <c r="J7" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="K7" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2300005053488464</v>
+        <v>0.2272142793577607</v>
       </c>
       <c r="M7" t="n">
-        <v>4.797228270171833</v>
+        <v>4.803240029456911</v>
       </c>
       <c r="N7" t="n">
-        <v>43.5341139882838</v>
+        <v>43.6215948927634</v>
       </c>
       <c r="O7" t="n">
-        <v>6.598038647074128</v>
+        <v>6.604664631361944</v>
       </c>
       <c r="P7" t="n">
-        <v>337.32138483452</v>
+        <v>337.3598492241338</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -23845,28 +23894,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.697175078487452</v>
+        <v>0.6901495223087271</v>
       </c>
       <c r="J8" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="K8" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1870616335404791</v>
+        <v>0.1839113988942559</v>
       </c>
       <c r="M8" t="n">
-        <v>7.68680836155825</v>
+        <v>7.694045386864579</v>
       </c>
       <c r="N8" t="n">
-        <v>122.7370777046625</v>
+        <v>123.0954059641926</v>
       </c>
       <c r="O8" t="n">
-        <v>11.07867671270637</v>
+        <v>11.09483690570495</v>
       </c>
       <c r="P8" t="n">
-        <v>330.8664620755848</v>
+        <v>330.9376535124796</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -23923,28 +23972,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8063886795930062</v>
+        <v>0.7986944425699521</v>
       </c>
       <c r="J9" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="K9" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2302039755533646</v>
+        <v>0.2265709256864391</v>
       </c>
       <c r="M9" t="n">
-        <v>8.006452428555811</v>
+        <v>8.007192489102769</v>
       </c>
       <c r="N9" t="n">
-        <v>126.3487243307299</v>
+        <v>126.8248733829387</v>
       </c>
       <c r="O9" t="n">
-        <v>11.24049484367703</v>
+        <v>11.2616550019497</v>
       </c>
       <c r="P9" t="n">
-        <v>327.8210951054965</v>
+        <v>327.8990624258831</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -24001,28 +24050,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3807104093289975</v>
+        <v>0.3747282106036241</v>
       </c>
       <c r="J10" t="n">
+        <v>450</v>
+      </c>
+      <c r="K10" t="n">
         <v>449</v>
       </c>
-      <c r="K10" t="n">
-        <v>448</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.08329182068375629</v>
+        <v>0.08087524586568939</v>
       </c>
       <c r="M10" t="n">
-        <v>6.792148549119241</v>
+        <v>6.807388827954777</v>
       </c>
       <c r="N10" t="n">
-        <v>92.85793649122418</v>
+        <v>93.10993323147463</v>
       </c>
       <c r="O10" t="n">
-        <v>9.636282296156759</v>
+        <v>9.649348850128419</v>
       </c>
       <c r="P10" t="n">
-        <v>332.2791514090351</v>
+        <v>332.3397357357114</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -24060,7 +24109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K450"/>
+  <dimension ref="A1:K451"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49685,6 +49734,63 @@
         </is>
       </c>
     </row>
+    <row r="451">
+      <c r="A451" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:19:36+00:00</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>-41.05101589371065,172.10678421726212</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>-41.050327709923344,172.10683300991025</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>-41.04965232194585,172.10675333273977</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>-41.04897032011036,172.1067399515695</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>-41.04828386753651,172.10677115882214</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>-41.04760486171566,172.1067275740236</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>-41.04692402684236,172.10670227175555</t>
+        </is>
+      </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>-41.04625088564791,172.1065997029645</t>
+        </is>
+      </c>
+      <c r="J451" t="inlineStr">
+        <is>
+          <t>-41.04557670307081,172.10650751422367</t>
+        </is>
+      </c>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0336/nzd0336.xlsx
+++ b/data/nzd0336/nzd0336.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K451"/>
+  <dimension ref="A1:K455"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18019,6 +18019,162 @@
         <v>327.92</v>
       </c>
       <c r="K451" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-31 22:19:26+00:00</t>
+        </is>
+      </c>
+      <c r="B452" t="n">
+        <v>386.45</v>
+      </c>
+      <c r="C452" t="n">
+        <v>372.37</v>
+      </c>
+      <c r="D452" t="n">
+        <v>368.43</v>
+      </c>
+      <c r="E452" t="n">
+        <v>359.72</v>
+      </c>
+      <c r="F452" t="n">
+        <v>345.64</v>
+      </c>
+      <c r="G452" t="n">
+        <v>340.25</v>
+      </c>
+      <c r="H452" t="n">
+        <v>333.56</v>
+      </c>
+      <c r="I452" t="n">
+        <v>330.27</v>
+      </c>
+      <c r="J452" t="n">
+        <v>329.98</v>
+      </c>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-01 22:13:04+00:00</t>
+        </is>
+      </c>
+      <c r="B453" t="n">
+        <v>388.14</v>
+      </c>
+      <c r="C453" t="n">
+        <v>373.81</v>
+      </c>
+      <c r="D453" t="n">
+        <v>370.56</v>
+      </c>
+      <c r="E453" t="n">
+        <v>361.5</v>
+      </c>
+      <c r="F453" t="n">
+        <v>346.39</v>
+      </c>
+      <c r="G453" t="n">
+        <v>341.36</v>
+      </c>
+      <c r="H453" t="n">
+        <v>335.51</v>
+      </c>
+      <c r="I453" t="n">
+        <v>330.27</v>
+      </c>
+      <c r="J453" t="n">
+        <v>329.98</v>
+      </c>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:19:13+00:00</t>
+        </is>
+      </c>
+      <c r="B454" t="n">
+        <v>386.49</v>
+      </c>
+      <c r="C454" t="n">
+        <v>375.23</v>
+      </c>
+      <c r="D454" t="n">
+        <v>373.95</v>
+      </c>
+      <c r="E454" t="n">
+        <v>364.9</v>
+      </c>
+      <c r="F454" t="n">
+        <v>349.27</v>
+      </c>
+      <c r="G454" t="n">
+        <v>345.13</v>
+      </c>
+      <c r="H454" t="n">
+        <v>338.34</v>
+      </c>
+      <c r="I454" t="n">
+        <v>333.53</v>
+      </c>
+      <c r="J454" t="n">
+        <v>334.78</v>
+      </c>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-16 22:19:21+00:00</t>
+        </is>
+      </c>
+      <c r="B455" t="n">
+        <v>385.4</v>
+      </c>
+      <c r="C455" t="n">
+        <v>374.67</v>
+      </c>
+      <c r="D455" t="n">
+        <v>373.36</v>
+      </c>
+      <c r="E455" t="n">
+        <v>364.62</v>
+      </c>
+      <c r="F455" t="n">
+        <v>348.74</v>
+      </c>
+      <c r="G455" t="n">
+        <v>345.15</v>
+      </c>
+      <c r="H455" t="n">
+        <v>338.15</v>
+      </c>
+      <c r="I455" t="n">
+        <v>333.37</v>
+      </c>
+      <c r="J455" t="n">
+        <v>335</v>
+      </c>
+      <c r="K455" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -18035,7 +18191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B522"/>
+  <dimension ref="A1:B526"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23258,6 +23414,46 @@
       </c>
       <c r="B522" t="n">
         <v>-0.1</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>2026-01-31 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B523" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>2026-02-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B524" t="n">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B525" t="n">
+        <v>-0.73</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>2026-02-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B526" t="n">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>
@@ -23426,28 +23622,28 @@
         <v>0.0861</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2978878384351051</v>
+        <v>0.3144345068091302</v>
       </c>
       <c r="J2" t="n">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="K2" t="n">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05452084257806145</v>
+        <v>0.0608348609363305</v>
       </c>
       <c r="M2" t="n">
-        <v>7.109372733900052</v>
+        <v>7.129830698485536</v>
       </c>
       <c r="N2" t="n">
-        <v>89.62346784354854</v>
+        <v>89.72277178460116</v>
       </c>
       <c r="O2" t="n">
-        <v>9.466967193539256</v>
+        <v>9.472210501493365</v>
       </c>
       <c r="P2" t="n">
-        <v>368.6020673778048</v>
+        <v>368.4335641122275</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -23504,28 +23700,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3948673421648608</v>
+        <v>0.4022871871233582</v>
       </c>
       <c r="J3" t="n">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="K3" t="n">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1037859411013426</v>
+        <v>0.1088298959560784</v>
       </c>
       <c r="M3" t="n">
-        <v>6.788478114333539</v>
+        <v>6.763780747996938</v>
       </c>
       <c r="N3" t="n">
-        <v>76.92132241927973</v>
+        <v>76.42152731460187</v>
       </c>
       <c r="O3" t="n">
-        <v>8.770480170394306</v>
+        <v>8.741940706422223</v>
       </c>
       <c r="P3" t="n">
-        <v>359.0983883857173</v>
+        <v>359.0216754580273</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23582,28 +23778,28 @@
         <v>0.1199</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2314087223911647</v>
+        <v>0.2295207059483621</v>
       </c>
       <c r="J4" t="n">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="K4" t="n">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03041878408977117</v>
+        <v>0.03045642555667027</v>
       </c>
       <c r="M4" t="n">
-        <v>6.230385719040849</v>
+        <v>6.19071910158522</v>
       </c>
       <c r="N4" t="n">
-        <v>98.02153385108873</v>
+        <v>97.20905878412971</v>
       </c>
       <c r="O4" t="n">
-        <v>9.900582500595039</v>
+        <v>9.859465441094143</v>
       </c>
       <c r="P4" t="n">
-        <v>366.5927532763199</v>
+        <v>366.6121628246716</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -23660,28 +23856,28 @@
         <v>0.0964</v>
       </c>
       <c r="I5" t="n">
-        <v>0.127909154367618</v>
+        <v>0.1318313525611957</v>
       </c>
       <c r="J5" t="n">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="K5" t="n">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01582410712398985</v>
+        <v>0.01706840808746335</v>
       </c>
       <c r="M5" t="n">
-        <v>5.737885897212609</v>
+        <v>5.712333234282874</v>
       </c>
       <c r="N5" t="n">
-        <v>59.33785947888155</v>
+        <v>58.90495417715324</v>
       </c>
       <c r="O5" t="n">
-        <v>7.703107131468545</v>
+        <v>7.674956298061458</v>
       </c>
       <c r="P5" t="n">
-        <v>356.8997002881936</v>
+        <v>356.8597332532323</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -23738,28 +23934,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5761392938484973</v>
+        <v>0.5678834748303411</v>
       </c>
       <c r="J6" t="n">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="K6" t="n">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3336533733192707</v>
+        <v>0.3298865905069899</v>
       </c>
       <c r="M6" t="n">
-        <v>4.821430461271814</v>
+        <v>4.821276160026549</v>
       </c>
       <c r="N6" t="n">
-        <v>38.60881506080794</v>
+        <v>38.5083530711869</v>
       </c>
       <c r="O6" t="n">
-        <v>6.213599203425334</v>
+        <v>6.205509896147689</v>
       </c>
       <c r="P6" t="n">
-        <v>337.3141131010304</v>
+        <v>337.3981737273107</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23816,28 +24012,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4692730758454123</v>
+        <v>0.4581553743651079</v>
       </c>
       <c r="J7" t="n">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="K7" t="n">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2272142793577607</v>
+        <v>0.2202738486766455</v>
       </c>
       <c r="M7" t="n">
-        <v>4.803240029456911</v>
+        <v>4.811069682469148</v>
       </c>
       <c r="N7" t="n">
-        <v>43.6215948927634</v>
+        <v>43.67747942697746</v>
       </c>
       <c r="O7" t="n">
-        <v>6.604664631361944</v>
+        <v>6.608893963968363</v>
       </c>
       <c r="P7" t="n">
-        <v>337.3598492241338</v>
+        <v>337.473045784226</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -23894,28 +24090,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6901495223087271</v>
+        <v>0.6692113348862805</v>
       </c>
       <c r="J8" t="n">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="K8" t="n">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1839113988942559</v>
+        <v>0.1757613687298507</v>
       </c>
       <c r="M8" t="n">
-        <v>7.694045386864579</v>
+        <v>7.702175123216256</v>
       </c>
       <c r="N8" t="n">
-        <v>123.0954059641926</v>
+        <v>123.4550765007144</v>
       </c>
       <c r="O8" t="n">
-        <v>11.09483690570495</v>
+        <v>11.11103399782011</v>
       </c>
       <c r="P8" t="n">
-        <v>330.9376535124796</v>
+        <v>331.1508676931915</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -23972,28 +24168,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7986944425699521</v>
+        <v>0.7706307310255364</v>
       </c>
       <c r="J9" t="n">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="K9" t="n">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2265709256864391</v>
+        <v>0.2139443883962405</v>
       </c>
       <c r="M9" t="n">
-        <v>8.007192489102769</v>
+        <v>8.006767679390247</v>
       </c>
       <c r="N9" t="n">
-        <v>126.8248733829387</v>
+        <v>128.2619554570462</v>
       </c>
       <c r="O9" t="n">
-        <v>11.2616550019497</v>
+        <v>11.32527948692862</v>
       </c>
       <c r="P9" t="n">
-        <v>327.8990624258831</v>
+        <v>328.1848479668088</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -24050,28 +24246,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3747282106036241</v>
+        <v>0.3586865073746529</v>
       </c>
       <c r="J10" t="n">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="K10" t="n">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="L10" t="n">
-        <v>0.08087524586568939</v>
+        <v>0.07519900199307727</v>
       </c>
       <c r="M10" t="n">
-        <v>6.807388827954777</v>
+        <v>6.828125926875963</v>
       </c>
       <c r="N10" t="n">
-        <v>93.10993323147463</v>
+        <v>93.17100619616615</v>
       </c>
       <c r="O10" t="n">
-        <v>9.649348850128419</v>
+        <v>9.652512947215671</v>
       </c>
       <c r="P10" t="n">
-        <v>332.3397357357114</v>
+        <v>332.5029851006349</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -24109,7 +24305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K451"/>
+  <dimension ref="A1:K455"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49791,6 +49987,234 @@
         </is>
       </c>
     </row>
+    <row r="452">
+      <c r="A452" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-31 22:19:26+00:00</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>-41.05101385987955,172.10680462601192</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>-41.050326287405014,172.10684728408748</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>-41.04965062903532,172.10677032001706</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>-41.04896935608888,172.1067496247798</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>-41.048281763131776,172.1067922745101</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>-41.04760437970114,172.1067324105281</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>-41.046925461131636,172.10668788035406</t>
+        </is>
+      </c>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>-41.0462505329551,172.10660324179779</t>
+        </is>
+      </c>
+      <c r="J452" t="inlineStr">
+        <is>
+          <t>-41.0455791248834,172.10648321448107</t>
+        </is>
+      </c>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-01 22:13:04+00:00</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>-41.05101584668571,172.10678468914074</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>-41.0503279803192,172.10683029663684</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>-41.04965313313126,172.10674519300244</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>-41.048971448719826,172.10672862683512</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>-41.04828264486607,172.10678342715497</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>-41.04760568466681,172.1067193165767</t>
+        </is>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>-41.046927753639466,172.1066648777029</t>
+        </is>
+      </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>-41.0462505329551,172.10660324179779</t>
+        </is>
+      </c>
+      <c r="J453" t="inlineStr">
+        <is>
+          <t>-41.0455791248834,172.10648321448107</t>
+        </is>
+      </c>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:19:13+00:00</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>-41.05101390690459,172.1068041541333</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>-41.05032964971821,172.1068135451222</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>-41.049657118512044,172.10670520211627</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>-41.04897544586936,172.10668851839793</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>-41.04828603071947,172.10674945330913</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>-41.04761011683634,172.10667484432355</t>
+        </is>
+      </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>-41.046931080706706,172.1066314943655</t>
+        </is>
+      </c>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>-41.0462543655445,172.10656478647425</t>
+        </is>
+      </c>
+      <c r="J454" t="inlineStr">
+        <is>
+          <t>-41.04558476792195,172.10642659371507</t>
+        </is>
+      </c>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-16 22:19:21+00:00</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>-41.051012625471635,172.1068170128248</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>-41.050328991363955,172.10682015135345</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>-41.04965642489219,172.1067121621823</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>-41.048975116692866,172.10669182144588</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>-41.04828540762914,172.10675570544075</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>-41.047610140349136,172.10667460839645</t>
+        </is>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>-41.046930857335006,172.10663373564972</t>
+        </is>
+      </c>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>-41.04625417744224,172.1065666738522</t>
+        </is>
+      </c>
+      <c r="J455" t="inlineStr">
+        <is>
+          <t>-41.045585026560545,172.10642399859643</t>
+        </is>
+      </c>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0336/nzd0336.xlsx
+++ b/data/nzd0336/nzd0336.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K455"/>
+  <dimension ref="A1:K457"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18175,6 +18175,84 @@
         <v>335</v>
       </c>
       <c r="K455" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:19:11+00:00</t>
+        </is>
+      </c>
+      <c r="B456" t="n">
+        <v>382.64</v>
+      </c>
+      <c r="C456" t="n">
+        <v>374.12</v>
+      </c>
+      <c r="D456" t="n">
+        <v>372.81</v>
+      </c>
+      <c r="E456" t="n">
+        <v>363.13</v>
+      </c>
+      <c r="F456" t="n">
+        <v>348.81</v>
+      </c>
+      <c r="G456" t="n">
+        <v>345.73</v>
+      </c>
+      <c r="H456" t="n">
+        <v>339.3</v>
+      </c>
+      <c r="I456" t="n">
+        <v>333.83</v>
+      </c>
+      <c r="J456" t="n">
+        <v>335.93</v>
+      </c>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:13:25+00:00</t>
+        </is>
+      </c>
+      <c r="B457" t="n">
+        <v>381.43</v>
+      </c>
+      <c r="C457" t="n">
+        <v>373.5</v>
+      </c>
+      <c r="D457" t="n">
+        <v>372.57</v>
+      </c>
+      <c r="E457" t="n">
+        <v>363.75</v>
+      </c>
+      <c r="F457" t="n">
+        <v>350.07</v>
+      </c>
+      <c r="G457" t="n">
+        <v>347.09</v>
+      </c>
+      <c r="H457" t="n">
+        <v>340.67</v>
+      </c>
+      <c r="I457" t="n">
+        <v>335.27</v>
+      </c>
+      <c r="J457" t="n">
+        <v>337.69</v>
+      </c>
+      <c r="K457" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -18191,7 +18269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B526"/>
+  <dimension ref="A1:B528"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23454,6 +23532,26 @@
       </c>
       <c r="B526" t="n">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B527" t="n">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B528" t="n">
+        <v>-0.04</v>
       </c>
     </row>
   </sheetData>
@@ -23622,28 +23720,28 @@
         <v>0.0861</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3144345068091302</v>
+        <v>0.3186978035482155</v>
       </c>
       <c r="J2" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K2" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0608348609363305</v>
+        <v>0.06283704647359933</v>
       </c>
       <c r="M2" t="n">
-        <v>7.129830698485536</v>
+        <v>7.119934958541809</v>
       </c>
       <c r="N2" t="n">
-        <v>89.72277178460116</v>
+        <v>89.45050956655324</v>
       </c>
       <c r="O2" t="n">
-        <v>9.472210501493365</v>
+        <v>9.45782795183721</v>
       </c>
       <c r="P2" t="n">
-        <v>368.4335641122275</v>
+        <v>368.3900010821257</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -23700,28 +23798,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4022871871233582</v>
+        <v>0.405674705063247</v>
       </c>
       <c r="J3" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K3" t="n">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1088298959560784</v>
+        <v>0.1112589062354745</v>
       </c>
       <c r="M3" t="n">
-        <v>6.763780747996938</v>
+        <v>6.7500429067856</v>
       </c>
       <c r="N3" t="n">
-        <v>76.42152731460187</v>
+        <v>76.15810655927622</v>
       </c>
       <c r="O3" t="n">
-        <v>8.741940706422223</v>
+        <v>8.726861208892704</v>
       </c>
       <c r="P3" t="n">
-        <v>359.0216754580273</v>
+        <v>358.9865407835353</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23778,28 +23876,28 @@
         <v>0.1199</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2295207059483621</v>
+        <v>0.2295072010043453</v>
       </c>
       <c r="J4" t="n">
+        <v>456</v>
+      </c>
+      <c r="K4" t="n">
         <v>454</v>
       </c>
-      <c r="K4" t="n">
-        <v>452</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.03045642555667027</v>
+        <v>0.03071946143849935</v>
       </c>
       <c r="M4" t="n">
-        <v>6.19071910158522</v>
+        <v>6.163978641142525</v>
       </c>
       <c r="N4" t="n">
-        <v>97.20905878412971</v>
+        <v>96.78089535637689</v>
       </c>
       <c r="O4" t="n">
-        <v>9.859465441094143</v>
+        <v>9.837728160321207</v>
       </c>
       <c r="P4" t="n">
-        <v>366.6121628246716</v>
+        <v>366.6123035073112</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -23856,28 +23954,28 @@
         <v>0.0964</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1318313525611957</v>
+        <v>0.1343296213252543</v>
       </c>
       <c r="J5" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K5" t="n">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01706840808746335</v>
+        <v>0.01785344391970645</v>
       </c>
       <c r="M5" t="n">
-        <v>5.712333234282874</v>
+        <v>5.701506508243353</v>
       </c>
       <c r="N5" t="n">
-        <v>58.90495417715324</v>
+        <v>58.68756604175153</v>
       </c>
       <c r="O5" t="n">
-        <v>7.674956298061458</v>
+        <v>7.660781033403286</v>
       </c>
       <c r="P5" t="n">
-        <v>356.8597332532323</v>
+        <v>356.8342013565975</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -23934,28 +24032,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5678834748303411</v>
+        <v>0.5654221292004995</v>
       </c>
       <c r="J6" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K6" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3298865905069899</v>
+        <v>0.3297024488108072</v>
       </c>
       <c r="M6" t="n">
-        <v>4.821276160026549</v>
+        <v>4.812733917023748</v>
       </c>
       <c r="N6" t="n">
-        <v>38.5083530711869</v>
+        <v>38.38100945549206</v>
       </c>
       <c r="O6" t="n">
-        <v>6.205509896147689</v>
+        <v>6.195240871466748</v>
       </c>
       <c r="P6" t="n">
-        <v>337.3981737273107</v>
+        <v>337.4233216798277</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -24012,28 +24110,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4581553743651079</v>
+        <v>0.4555393582669928</v>
       </c>
       <c r="J7" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K7" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2202738486766455</v>
+        <v>0.2196568052348811</v>
       </c>
       <c r="M7" t="n">
-        <v>4.811069682469148</v>
+        <v>4.801943467349703</v>
       </c>
       <c r="N7" t="n">
-        <v>43.67747942697746</v>
+        <v>43.53295274552338</v>
       </c>
       <c r="O7" t="n">
-        <v>6.608893963968363</v>
+        <v>6.597950647399796</v>
       </c>
       <c r="P7" t="n">
-        <v>337.473045784226</v>
+        <v>337.4997738669189</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -24090,28 +24188,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6692113348862805</v>
+        <v>0.6619701944137262</v>
       </c>
       <c r="J8" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K8" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1757613687298507</v>
+        <v>0.1735070683887427</v>
       </c>
       <c r="M8" t="n">
-        <v>7.702175123216256</v>
+        <v>7.695148049058452</v>
       </c>
       <c r="N8" t="n">
-        <v>123.4550765007144</v>
+        <v>123.2605701907062</v>
       </c>
       <c r="O8" t="n">
-        <v>11.11103399782011</v>
+        <v>11.10227770282775</v>
       </c>
       <c r="P8" t="n">
-        <v>331.1508676931915</v>
+        <v>331.2248622714984</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -24168,28 +24266,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7706307310255364</v>
+        <v>0.7592002943502312</v>
       </c>
       <c r="J9" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K9" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2139443883962405</v>
+        <v>0.2093270066922468</v>
       </c>
       <c r="M9" t="n">
-        <v>8.006767679390247</v>
+        <v>8.001170285120599</v>
       </c>
       <c r="N9" t="n">
-        <v>128.2619554570462</v>
+        <v>128.5611376740262</v>
       </c>
       <c r="O9" t="n">
-        <v>11.32527948692862</v>
+        <v>11.33848039527459</v>
       </c>
       <c r="P9" t="n">
-        <v>328.1848479668088</v>
+        <v>328.3016547567148</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -24246,28 +24344,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3586865073746529</v>
+        <v>0.3544564557406891</v>
       </c>
       <c r="J10" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K10" t="n">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="L10" t="n">
-        <v>0.07519900199307727</v>
+        <v>0.07408657153745091</v>
       </c>
       <c r="M10" t="n">
-        <v>6.828125926875963</v>
+        <v>6.819736767108046</v>
       </c>
       <c r="N10" t="n">
-        <v>93.17100619616615</v>
+        <v>92.88289900368738</v>
       </c>
       <c r="O10" t="n">
-        <v>9.652512947215671</v>
+        <v>9.637577444756923</v>
       </c>
       <c r="P10" t="n">
-        <v>332.5029851006349</v>
+        <v>332.5461826633045</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -24305,7 +24403,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K455"/>
+  <dimension ref="A1:K457"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50215,6 +50313,120 @@
         </is>
       </c>
     </row>
+    <row r="456">
+      <c r="A456" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:19:11+00:00</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>-41.05100938073584,172.10684957244513</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>-41.05032834476567,172.10682663961612</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>-41.04965577829705,172.10671865037938</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>-41.04897336500208,172.10670939837905</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>-41.048285489924126,172.10675487968751</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>-41.04761082221983,172.10666776651084</t>
+        </is>
+      </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>-41.04693220932095,172.10662016998174</t>
+        </is>
+      </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>-41.04625471823612,172.10656124764057</t>
+        </is>
+      </c>
+      <c r="J456" t="inlineStr">
+        <is>
+          <t>-41.04558611989579,172.10641302832187</t>
+        </is>
+      </c>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:13:25+00:00</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>-41.051007958221945,172.10686384677047</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>-41.05032761587261,172.10683395365754</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>-41.04965549614632,172.10672148159261</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>-41.04897409389388,172.1067020844875</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>-41.048286971232514,172.10674001612915</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>-41.04761242108744,172.1066517234682</t>
+        </is>
+      </c>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>-41.046933819945615,172.10660400914182</t>
+        </is>
+      </c>
+      <c r="I457" t="inlineStr">
+        <is>
+          <t>-41.04625641115443,172.1065442612385</t>
+        </is>
+      </c>
+      <c r="J457" t="inlineStr">
+        <is>
+          <t>-41.04558818900047,172.1063922673712</t>
+        </is>
+      </c>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0336/nzd0336.xlsx
+++ b/data/nzd0336/nzd0336.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K457"/>
+  <dimension ref="A1:K460"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18253,6 +18253,123 @@
         <v>337.69</v>
       </c>
       <c r="K457" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:12:46+00:00</t>
+        </is>
+      </c>
+      <c r="B458" t="n">
+        <v>380.04</v>
+      </c>
+      <c r="C458" t="n">
+        <v>372.75</v>
+      </c>
+      <c r="D458" t="n">
+        <v>372.71</v>
+      </c>
+      <c r="E458" t="n">
+        <v>364.23</v>
+      </c>
+      <c r="F458" t="n">
+        <v>351.07</v>
+      </c>
+      <c r="G458" t="n">
+        <v>348.04</v>
+      </c>
+      <c r="H458" t="n">
+        <v>343.99</v>
+      </c>
+      <c r="I458" t="n">
+        <v>338.63</v>
+      </c>
+      <c r="J458" t="n">
+        <v>340.97</v>
+      </c>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:12:47+00:00</t>
+        </is>
+      </c>
+      <c r="B459" t="n">
+        <v>381.05</v>
+      </c>
+      <c r="C459" t="n">
+        <v>373.69</v>
+      </c>
+      <c r="D459" t="n">
+        <v>374.13</v>
+      </c>
+      <c r="E459" t="n">
+        <v>367.02</v>
+      </c>
+      <c r="F459" t="n">
+        <v>354.85</v>
+      </c>
+      <c r="G459" t="n">
+        <v>350.74</v>
+      </c>
+      <c r="H459" t="n">
+        <v>346.7</v>
+      </c>
+      <c r="I459" t="n">
+        <v>341.32</v>
+      </c>
+      <c r="J459" t="n">
+        <v>344.44</v>
+      </c>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:18:57+00:00</t>
+        </is>
+      </c>
+      <c r="B460" t="n">
+        <v>380.78</v>
+      </c>
+      <c r="C460" t="n">
+        <v>373.9</v>
+      </c>
+      <c r="D460" t="n">
+        <v>374.33</v>
+      </c>
+      <c r="E460" t="n">
+        <v>367.48</v>
+      </c>
+      <c r="F460" t="n">
+        <v>355.93</v>
+      </c>
+      <c r="G460" t="n">
+        <v>351.4</v>
+      </c>
+      <c r="H460" t="n">
+        <v>347.66</v>
+      </c>
+      <c r="I460" t="n">
+        <v>342.12</v>
+      </c>
+      <c r="J460" t="n">
+        <v>345.56</v>
+      </c>
+      <c r="K460" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -18269,7 +18386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B528"/>
+  <dimension ref="A1:B531"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23552,6 +23669,36 @@
       </c>
       <c r="B528" t="n">
         <v>-0.04</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B529" t="n">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B530" t="n">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B531" t="n">
+        <v>-0.32</v>
       </c>
     </row>
   </sheetData>
@@ -23720,28 +23867,28 @@
         <v>0.0861</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3186978035482155</v>
+        <v>0.3231994725184988</v>
       </c>
       <c r="J2" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="K2" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06283704647359933</v>
+        <v>0.06525706278487708</v>
       </c>
       <c r="M2" t="n">
-        <v>7.119934958541809</v>
+        <v>7.095730580979759</v>
       </c>
       <c r="N2" t="n">
-        <v>89.45050956655324</v>
+        <v>88.95663728922146</v>
       </c>
       <c r="O2" t="n">
-        <v>9.45782795183721</v>
+        <v>9.43168263297814</v>
       </c>
       <c r="P2" t="n">
-        <v>368.3900010821257</v>
+        <v>368.3437775574662</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -23798,28 +23945,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.405674705063247</v>
+        <v>0.4101424352502717</v>
       </c>
       <c r="J3" t="n">
+        <v>459</v>
+      </c>
+      <c r="K3" t="n">
         <v>456</v>
       </c>
-      <c r="K3" t="n">
-        <v>453</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.1112589062354745</v>
+        <v>0.1146851243053875</v>
       </c>
       <c r="M3" t="n">
-        <v>6.7500429067856</v>
+        <v>6.726576406304855</v>
       </c>
       <c r="N3" t="n">
-        <v>76.15810655927622</v>
+        <v>75.74458225277486</v>
       </c>
       <c r="O3" t="n">
-        <v>8.726861208892704</v>
+        <v>8.703136345753459</v>
       </c>
       <c r="P3" t="n">
-        <v>358.9865407835353</v>
+        <v>358.9399786419844</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23876,28 +24023,28 @@
         <v>0.1199</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2295072010043453</v>
+        <v>0.230720820854895</v>
       </c>
       <c r="J4" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="K4" t="n">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03071946143849935</v>
+        <v>0.03143815970809705</v>
       </c>
       <c r="M4" t="n">
-        <v>6.163978641142525</v>
+        <v>6.131860283624087</v>
       </c>
       <c r="N4" t="n">
-        <v>96.78089535637689</v>
+        <v>96.15524640280977</v>
       </c>
       <c r="O4" t="n">
-        <v>9.837728160321207</v>
+        <v>9.805878155617158</v>
       </c>
       <c r="P4" t="n">
-        <v>366.6123035073112</v>
+        <v>366.599695233485</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -23954,28 +24101,28 @@
         <v>0.0964</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1343296213252543</v>
+        <v>0.1413468185299918</v>
       </c>
       <c r="J5" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="K5" t="n">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01785344391970645</v>
+        <v>0.01991165472527456</v>
       </c>
       <c r="M5" t="n">
-        <v>5.701506508243353</v>
+        <v>5.703870927265523</v>
       </c>
       <c r="N5" t="n">
-        <v>58.68756604175153</v>
+        <v>58.53461596488993</v>
       </c>
       <c r="O5" t="n">
-        <v>7.660781033403286</v>
+        <v>7.650791852147719</v>
       </c>
       <c r="P5" t="n">
-        <v>356.8342013565975</v>
+        <v>356.7621341853269</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -24032,28 +24179,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5654221292004995</v>
+        <v>0.5671934586795391</v>
       </c>
       <c r="J6" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="K6" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3297024488108072</v>
+        <v>0.3338060379717922</v>
       </c>
       <c r="M6" t="n">
-        <v>4.812733917023748</v>
+        <v>4.797320864711722</v>
       </c>
       <c r="N6" t="n">
-        <v>38.38100945549206</v>
+        <v>38.17168507442933</v>
       </c>
       <c r="O6" t="n">
-        <v>6.195240871466748</v>
+        <v>6.178323807832456</v>
       </c>
       <c r="P6" t="n">
-        <v>337.4233216798277</v>
+        <v>337.4050919245749</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -24110,28 +24257,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4555393582669928</v>
+        <v>0.4560537812110101</v>
       </c>
       <c r="J7" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="K7" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2196568052348811</v>
+        <v>0.2222840376903565</v>
       </c>
       <c r="M7" t="n">
-        <v>4.801943467349703</v>
+        <v>4.780582691559811</v>
       </c>
       <c r="N7" t="n">
-        <v>43.53295274552338</v>
+        <v>43.26306244360096</v>
       </c>
       <c r="O7" t="n">
-        <v>6.597950647399796</v>
+        <v>6.577466263205077</v>
       </c>
       <c r="P7" t="n">
-        <v>337.4997738669189</v>
+        <v>337.4944614702512</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -24188,28 +24335,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6619701944137262</v>
+        <v>0.6586742047654486</v>
       </c>
       <c r="J8" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="K8" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1735070683887427</v>
+        <v>0.1739149683788599</v>
       </c>
       <c r="M8" t="n">
-        <v>7.695148049058452</v>
+        <v>7.657003868025077</v>
       </c>
       <c r="N8" t="n">
-        <v>123.2605701907062</v>
+        <v>122.5184526460579</v>
       </c>
       <c r="O8" t="n">
-        <v>11.10227770282775</v>
+        <v>11.06880538477653</v>
       </c>
       <c r="P8" t="n">
-        <v>331.2248622714984</v>
+        <v>331.258666787149</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -24266,28 +24413,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7592002943502312</v>
+        <v>0.7497758403535408</v>
       </c>
       <c r="J9" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="K9" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2093270066922468</v>
+        <v>0.2068836552014232</v>
       </c>
       <c r="M9" t="n">
-        <v>8.001170285120599</v>
+        <v>7.973472264483347</v>
       </c>
       <c r="N9" t="n">
-        <v>128.5611376740262</v>
+        <v>128.1285775423185</v>
       </c>
       <c r="O9" t="n">
-        <v>11.33848039527459</v>
+        <v>11.31938945095178</v>
       </c>
       <c r="P9" t="n">
-        <v>328.3016547567148</v>
+        <v>328.3983772224396</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -24344,28 +24491,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3544564557406891</v>
+        <v>0.3564710243669961</v>
       </c>
       <c r="J10" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="K10" t="n">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="L10" t="n">
-        <v>0.07408657153745091</v>
+        <v>0.07576416103485217</v>
       </c>
       <c r="M10" t="n">
-        <v>6.819736767108046</v>
+        <v>6.79090532861138</v>
       </c>
       <c r="N10" t="n">
-        <v>92.88289900368738</v>
+        <v>92.31704088715999</v>
       </c>
       <c r="O10" t="n">
-        <v>9.637577444756923</v>
+        <v>9.608175731488261</v>
       </c>
       <c r="P10" t="n">
-        <v>332.5461826633045</v>
+        <v>332.52546903051</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -24403,7 +24550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K457"/>
+  <dimension ref="A1:K460"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50427,6 +50574,177 @@
         </is>
       </c>
     </row>
+    <row r="458">
+      <c r="A458" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:12:46+00:00</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>-41.05100632409224,172.10688024454845</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>-41.0503267341465,172.10684280128808</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>-41.04965566073425,172.10671983005156</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>-41.048974658196876,172.10669642211974</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>-41.04828814687272,172.1067282196538</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>-41.04761353794217,172.1066405169306</t>
+        </is>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>-41.04693772305576,172.10656484564342</t>
+        </is>
+      </c>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>-41.046260361287345,172.10650462629704</t>
+        </is>
+      </c>
+      <c r="J458" t="inlineStr">
+        <is>
+          <t>-41.04559204504917,172.10635357650537</t>
+        </is>
+      </c>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:12:47+00:00</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>-41.0510075114817,172.10686832961633</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>-41.05032783924311,172.10683171225776</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>-41.04965733012479,172.10670307870626</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>-41.04897793820257,172.10666350960537</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>-41.04829259078179,172.10668362897343</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>-41.04761671215489,172.10660866676926</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>-41.046940909018296,172.10653287784476</t>
+        </is>
+      </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>-41.046263523735085,172.1064728947484</t>
+        </is>
+      </c>
+      <c r="J459" t="inlineStr">
+        <is>
+          <t>-41.045596124452345,172.10631264439567</t>
+        </is>
+      </c>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:18:57+00:00</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>-41.05100719406087,172.10687151479624</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>-41.05032808612625,172.10682923492115</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>-41.049657565250016,172.10670071936175</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>-41.04897847899113,172.10665808316898</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>-41.04829386046692,172.106670888778</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>-41.047617488072206,172.1066008811738</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>-41.046942037622806,172.10652155345784</t>
+        </is>
+      </c>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>-41.04626446423831,172.10646345785608</t>
+        </is>
+      </c>
+      <c r="J460" t="inlineStr">
+        <is>
+          <t>-41.04559744114421,172.10629943287796</t>
+        </is>
+      </c>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0336/nzd0336.xlsx
+++ b/data/nzd0336/nzd0336.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K460"/>
+  <dimension ref="A1:K463"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18370,6 +18370,123 @@
         <v>345.56</v>
       </c>
       <c r="K460" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:12:32+00:00</t>
+        </is>
+      </c>
+      <c r="B461" t="n">
+        <v>380.74</v>
+      </c>
+      <c r="C461" t="n">
+        <v>374.63</v>
+      </c>
+      <c r="D461" t="n">
+        <v>374.97</v>
+      </c>
+      <c r="E461" t="n">
+        <v>368.12</v>
+      </c>
+      <c r="F461" t="n">
+        <v>357.2</v>
+      </c>
+      <c r="G461" t="n">
+        <v>352.57</v>
+      </c>
+      <c r="H461" t="n">
+        <v>349.33</v>
+      </c>
+      <c r="I461" t="n">
+        <v>343.18</v>
+      </c>
+      <c r="J461" t="n">
+        <v>346.58</v>
+      </c>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:13:06+00:00</t>
+        </is>
+      </c>
+      <c r="B462" t="n">
+        <v>379.25</v>
+      </c>
+      <c r="C462" t="n">
+        <v>373.83</v>
+      </c>
+      <c r="D462" t="n">
+        <v>374.93</v>
+      </c>
+      <c r="E462" t="n">
+        <v>368.46</v>
+      </c>
+      <c r="F462" t="n">
+        <v>357.76</v>
+      </c>
+      <c r="G462" t="n">
+        <v>353.28</v>
+      </c>
+      <c r="H462" t="n">
+        <v>349.49</v>
+      </c>
+      <c r="I462" t="n">
+        <v>343.05</v>
+      </c>
+      <c r="J462" t="n">
+        <v>346.93</v>
+      </c>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:12:25+00:00</t>
+        </is>
+      </c>
+      <c r="B463" t="n">
+        <v>377.67</v>
+      </c>
+      <c r="C463" t="n">
+        <v>373.01</v>
+      </c>
+      <c r="D463" t="n">
+        <v>374.25</v>
+      </c>
+      <c r="E463" t="n">
+        <v>368.45</v>
+      </c>
+      <c r="F463" t="n">
+        <v>358.28</v>
+      </c>
+      <c r="G463" t="n">
+        <v>353.17</v>
+      </c>
+      <c r="H463" t="n">
+        <v>350.82</v>
+      </c>
+      <c r="I463" t="n">
+        <v>345.41</v>
+      </c>
+      <c r="J463" t="n">
+        <v>350.12</v>
+      </c>
+      <c r="K463" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -18386,7 +18503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B531"/>
+  <dimension ref="A1:B534"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23699,6 +23816,36 @@
       </c>
       <c r="B531" t="n">
         <v>-0.32</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B532" t="n">
+        <v>-0.82</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B533" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B534" t="n">
+        <v>1.75</v>
       </c>
     </row>
   </sheetData>
@@ -23867,28 +24014,28 @@
         <v>0.0861</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3231994725184988</v>
+        <v>0.3258545388763811</v>
       </c>
       <c r="J2" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="K2" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06525706278487708</v>
+        <v>0.06705095863110466</v>
       </c>
       <c r="M2" t="n">
-        <v>7.095730580979759</v>
+        <v>7.062825850319388</v>
       </c>
       <c r="N2" t="n">
-        <v>88.95663728922146</v>
+        <v>88.42129399543551</v>
       </c>
       <c r="O2" t="n">
-        <v>9.43168263297814</v>
+        <v>9.403259753693689</v>
       </c>
       <c r="P2" t="n">
-        <v>368.3437775574662</v>
+        <v>368.3164527362117</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -23945,28 +24092,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4101424352502717</v>
+        <v>0.4148798543471212</v>
       </c>
       <c r="J3" t="n">
+        <v>462</v>
+      </c>
+      <c r="K3" t="n">
         <v>459</v>
       </c>
-      <c r="K3" t="n">
-        <v>456</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.1146851243053875</v>
+        <v>0.1182734073031364</v>
       </c>
       <c r="M3" t="n">
-        <v>6.726576406304855</v>
+        <v>6.70473042566378</v>
       </c>
       <c r="N3" t="n">
-        <v>75.74458225277486</v>
+        <v>75.35131293535433</v>
       </c>
       <c r="O3" t="n">
-        <v>8.703136345753459</v>
+        <v>8.68051340275184</v>
       </c>
       <c r="P3" t="n">
-        <v>358.9399786419844</v>
+        <v>358.8904724870388</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -24023,28 +24170,28 @@
         <v>0.1199</v>
       </c>
       <c r="I4" t="n">
-        <v>0.230720820854895</v>
+        <v>0.2330657783705632</v>
       </c>
       <c r="J4" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="K4" t="n">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03143815970809705</v>
+        <v>0.03246472366818098</v>
       </c>
       <c r="M4" t="n">
-        <v>6.131860283624087</v>
+        <v>6.107807576428368</v>
       </c>
       <c r="N4" t="n">
-        <v>96.15524640280977</v>
+        <v>95.55328586568217</v>
       </c>
       <c r="O4" t="n">
-        <v>9.805878155617158</v>
+        <v>9.775136104713948</v>
       </c>
       <c r="P4" t="n">
-        <v>366.599695233485</v>
+        <v>366.5752918153976</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -24101,28 +24248,28 @@
         <v>0.0964</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1413468185299918</v>
+        <v>0.150612296438863</v>
       </c>
       <c r="J5" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="K5" t="n">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01991165472527456</v>
+        <v>0.02269002454053215</v>
       </c>
       <c r="M5" t="n">
-        <v>5.703870927265523</v>
+        <v>5.719755513308105</v>
       </c>
       <c r="N5" t="n">
-        <v>58.53461596488993</v>
+        <v>58.54269734241234</v>
       </c>
       <c r="O5" t="n">
-        <v>7.650791852147719</v>
+        <v>7.651319973861526</v>
       </c>
       <c r="P5" t="n">
-        <v>356.7621341853269</v>
+        <v>356.6667105877967</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -24179,28 +24326,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5671934586795391</v>
+        <v>0.5733619945491629</v>
       </c>
       <c r="J6" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="K6" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3338060379717922</v>
+        <v>0.3405632376060687</v>
       </c>
       <c r="M6" t="n">
-        <v>4.797320864711722</v>
+        <v>4.800986352421607</v>
       </c>
       <c r="N6" t="n">
-        <v>38.17168507442933</v>
+        <v>38.09689479612018</v>
       </c>
       <c r="O6" t="n">
-        <v>6.178323807832456</v>
+        <v>6.17226820513498</v>
       </c>
       <c r="P6" t="n">
-        <v>337.4050919245749</v>
+        <v>337.341554374671</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -24257,28 +24404,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4560537812110101</v>
+        <v>0.4600084655760253</v>
       </c>
       <c r="J7" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="K7" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2222840376903565</v>
+        <v>0.227296850418082</v>
       </c>
       <c r="M7" t="n">
-        <v>4.780582691559811</v>
+        <v>4.773880172708939</v>
       </c>
       <c r="N7" t="n">
-        <v>43.26306244360096</v>
+        <v>43.05338454330048</v>
       </c>
       <c r="O7" t="n">
-        <v>6.577466263205077</v>
+        <v>6.561507794958448</v>
       </c>
       <c r="P7" t="n">
-        <v>337.4944614702512</v>
+        <v>337.4537284090177</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -24335,28 +24482,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6586742047654486</v>
+        <v>0.6598964801958931</v>
       </c>
       <c r="J8" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="K8" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1739149683788599</v>
+        <v>0.1763397007623707</v>
       </c>
       <c r="M8" t="n">
-        <v>7.657003868025077</v>
+        <v>7.61591858382589</v>
       </c>
       <c r="N8" t="n">
-        <v>122.5184526460579</v>
+        <v>121.7323603766289</v>
       </c>
       <c r="O8" t="n">
-        <v>11.06880538477653</v>
+        <v>11.03323888876829</v>
       </c>
       <c r="P8" t="n">
-        <v>331.258666787149</v>
+        <v>331.246068099518</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -24413,28 +24560,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7497758403535408</v>
+        <v>0.7443844714815587</v>
       </c>
       <c r="J9" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="K9" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2068836552014232</v>
+        <v>0.2064953707043867</v>
       </c>
       <c r="M9" t="n">
-        <v>7.973472264483347</v>
+        <v>7.935535579894929</v>
       </c>
       <c r="N9" t="n">
-        <v>128.1285775423185</v>
+        <v>127.4354156544654</v>
       </c>
       <c r="O9" t="n">
-        <v>11.31938945095178</v>
+        <v>11.28872958549656</v>
       </c>
       <c r="P9" t="n">
-        <v>328.3983772224396</v>
+        <v>328.453887929244</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -24491,28 +24638,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3564710243669961</v>
+        <v>0.3633956762974737</v>
       </c>
       <c r="J10" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="K10" t="n">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="L10" t="n">
-        <v>0.07576416103485217</v>
+        <v>0.07927336542014829</v>
       </c>
       <c r="M10" t="n">
-        <v>6.79090532861138</v>
+        <v>6.786021701951654</v>
       </c>
       <c r="N10" t="n">
-        <v>92.31704088715999</v>
+        <v>91.94956900420753</v>
       </c>
       <c r="O10" t="n">
-        <v>9.608175731488261</v>
+        <v>9.589033788876099</v>
       </c>
       <c r="P10" t="n">
-        <v>332.52546903051</v>
+        <v>332.4541622449149</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -24550,7 +24697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K460"/>
+  <dimension ref="A1:K463"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50745,6 +50892,177 @@
         </is>
       </c>
     </row>
+    <row r="461">
+      <c r="A461" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:12:32+00:00</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>-41.05100714703555,172.10687198667475</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>-41.050328944338645,172.1068206232271</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>-41.04965831765044,172.10669316945936</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>-41.04897923139218,172.10665053334435</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>-41.04829535352077,172.1066559072513</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>-41.04761886356071,172.10658707943597</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>-41.04694400092176,172.10650185374215</t>
+        </is>
+      </c>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>-41.04626571040387,172.1064509539733</t>
+        </is>
+      </c>
+      <c r="J461" t="inlineStr">
+        <is>
+          <t>-41.04559864027298,172.10628740095962</t>
+        </is>
+      </c>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:13:06+00:00</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>-41.05100539534121,172.10688956414856</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>-41.05032800383187,172.10683006070005</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>-41.049658270625415,172.10669364132826</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>-41.048979631105034,172.10664652249994</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>-41.048296011874605,172.10664930122354</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>-41.047619698258046,172.10657870402216</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>-41.046944189022085,172.1064999663442</t>
+        </is>
+      </c>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>-41.04626555757232,172.1064524874684</t>
+        </is>
+      </c>
+      <c r="J462" t="inlineStr">
+        <is>
+          <t>-41.04559905173844,172.1062832723601</t>
+        </is>
+      </c>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:12:25+00:00</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>-41.05100353783689,172.10690820334798</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>-41.05032703981163,172.1068397341095</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>-41.04965747119993,172.10670166309956</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>-41.048979619348785,172.10664664046595</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>-41.04829662320283,172.10664316705484</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>-41.04761956893878,172.1065800016215</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>-41.046945752604785,172.10648427734822</t>
+        </is>
+      </c>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>-41.04626833204963,172.10642464863363</t>
+        </is>
+      </c>
+      <c r="J463" t="inlineStr">
+        <is>
+          <t>-41.045602801945385,172.10624564312215</t>
+        </is>
+      </c>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0336/nzd0336.xlsx
+++ b/data/nzd0336/nzd0336.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K463"/>
+  <dimension ref="A1:K468"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18487,6 +18487,201 @@
         <v>350.12</v>
       </c>
       <c r="K463" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-24 22:12:29+00:00</t>
+        </is>
+      </c>
+      <c r="B464" t="n">
+        <v>376.43</v>
+      </c>
+      <c r="C464" t="n">
+        <v>372.24</v>
+      </c>
+      <c r="D464" t="n">
+        <v>374.87</v>
+      </c>
+      <c r="E464" t="n">
+        <v>368.7</v>
+      </c>
+      <c r="F464" t="n">
+        <v>359.65</v>
+      </c>
+      <c r="G464" t="n">
+        <v>354.73</v>
+      </c>
+      <c r="H464" t="n">
+        <v>352.81</v>
+      </c>
+      <c r="I464" t="n">
+        <v>347.37</v>
+      </c>
+      <c r="J464" t="n">
+        <v>352.11</v>
+      </c>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:18:27+00:00</t>
+        </is>
+      </c>
+      <c r="B465" t="n">
+        <v>377.14</v>
+      </c>
+      <c r="C465" t="n">
+        <v>374.56</v>
+      </c>
+      <c r="D465" t="n">
+        <v>375.4</v>
+      </c>
+      <c r="E465" t="n">
+        <v>369.76</v>
+      </c>
+      <c r="F465" t="n">
+        <v>360.67</v>
+      </c>
+      <c r="G465" t="n">
+        <v>355.55</v>
+      </c>
+      <c r="H465" t="n">
+        <v>353.79</v>
+      </c>
+      <c r="I465" t="n">
+        <v>347.71</v>
+      </c>
+      <c r="J465" t="n">
+        <v>353.34</v>
+      </c>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:12:05+00:00</t>
+        </is>
+      </c>
+      <c r="B466" t="n">
+        <v>377.14</v>
+      </c>
+      <c r="C466" t="n">
+        <v>374.77</v>
+      </c>
+      <c r="D466" t="n">
+        <v>375.09</v>
+      </c>
+      <c r="E466" t="n">
+        <v>369.62</v>
+      </c>
+      <c r="F466" t="n">
+        <v>362.42</v>
+      </c>
+      <c r="G466" t="n">
+        <v>355.72</v>
+      </c>
+      <c r="H466" t="n">
+        <v>352.7</v>
+      </c>
+      <c r="I466" t="n">
+        <v>346.29</v>
+      </c>
+      <c r="J466" t="n">
+        <v>353.34</v>
+      </c>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:12:23+00:00</t>
+        </is>
+      </c>
+      <c r="B467" t="n">
+        <v>384.33</v>
+      </c>
+      <c r="C467" t="n">
+        <v>374.77</v>
+      </c>
+      <c r="D467" t="n">
+        <v>375.09</v>
+      </c>
+      <c r="E467" t="n">
+        <v>369.62</v>
+      </c>
+      <c r="F467" t="n">
+        <v>367.63</v>
+      </c>
+      <c r="G467" t="n">
+        <v>361.2</v>
+      </c>
+      <c r="H467" t="n">
+        <v>352.7</v>
+      </c>
+      <c r="I467" t="n">
+        <v>346.29</v>
+      </c>
+      <c r="J467" t="n">
+        <v>353.34</v>
+      </c>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:18:38+00:00</t>
+        </is>
+      </c>
+      <c r="B468" t="n">
+        <v>384.33</v>
+      </c>
+      <c r="C468" t="n">
+        <v>374.77</v>
+      </c>
+      <c r="D468" t="n">
+        <v>375.09</v>
+      </c>
+      <c r="E468" t="n">
+        <v>369.62</v>
+      </c>
+      <c r="F468" t="n">
+        <v>367.63</v>
+      </c>
+      <c r="G468" t="n">
+        <v>361.2</v>
+      </c>
+      <c r="H468" t="n">
+        <v>350.97</v>
+      </c>
+      <c r="I468" t="n">
+        <v>344.23</v>
+      </c>
+      <c r="J468" t="n">
+        <v>348.87</v>
+      </c>
+      <c r="K468" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -18503,7 +18698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B534"/>
+  <dimension ref="A1:B539"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23846,6 +24041,56 @@
       </c>
       <c r="B534" t="n">
         <v>1.75</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>2026-05-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B535" t="n">
+        <v>-0.62</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B536" t="n">
+        <v>-0.93</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B537" t="n">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B538" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B539" t="n">
+        <v>-0.2</v>
       </c>
     </row>
   </sheetData>
@@ -24014,28 +24259,28 @@
         <v>0.0861</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3258545388763811</v>
+        <v>0.3313215657744775</v>
       </c>
       <c r="J2" t="n">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="K2" t="n">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06705095863110466</v>
+        <v>0.07039815327762189</v>
       </c>
       <c r="M2" t="n">
-        <v>7.062825850319388</v>
+        <v>7.01658143875147</v>
       </c>
       <c r="N2" t="n">
-        <v>88.42129399543551</v>
+        <v>87.69858267864041</v>
       </c>
       <c r="O2" t="n">
-        <v>9.403259753693689</v>
+        <v>9.364752141869021</v>
       </c>
       <c r="P2" t="n">
-        <v>368.3164527362117</v>
+        <v>368.2597754672477</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -24092,28 +24337,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4148798543471212</v>
+        <v>0.423149672274642</v>
       </c>
       <c r="J3" t="n">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="K3" t="n">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1182734073031364</v>
+        <v>0.1245236151597341</v>
       </c>
       <c r="M3" t="n">
-        <v>6.70473042566378</v>
+        <v>6.67076756588593</v>
       </c>
       <c r="N3" t="n">
-        <v>75.35131293535433</v>
+        <v>74.73424114703313</v>
       </c>
       <c r="O3" t="n">
-        <v>8.68051340275184</v>
+        <v>8.644896826858787</v>
       </c>
       <c r="P3" t="n">
-        <v>358.8904724870388</v>
+        <v>358.8035783476442</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -24170,28 +24415,28 @@
         <v>0.1199</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2330657783705632</v>
+        <v>0.2375366394672186</v>
       </c>
       <c r="J4" t="n">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="K4" t="n">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03246472366818098</v>
+        <v>0.03437446780391185</v>
       </c>
       <c r="M4" t="n">
-        <v>6.107807576428368</v>
+        <v>6.072146628032876</v>
       </c>
       <c r="N4" t="n">
-        <v>95.55328586568217</v>
+        <v>94.58047403572331</v>
       </c>
       <c r="O4" t="n">
-        <v>9.775136104713948</v>
+        <v>9.725249304553756</v>
       </c>
       <c r="P4" t="n">
-        <v>366.5752918153976</v>
+        <v>366.5285195900095</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -24248,28 +24493,28 @@
         <v>0.0964</v>
       </c>
       <c r="I5" t="n">
-        <v>0.150612296438863</v>
+        <v>0.1675523160497347</v>
       </c>
       <c r="J5" t="n">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="K5" t="n">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02269002454053215</v>
+        <v>0.02814502304186872</v>
       </c>
       <c r="M5" t="n">
-        <v>5.719755513308105</v>
+        <v>5.758136138222714</v>
       </c>
       <c r="N5" t="n">
-        <v>58.54269734241234</v>
+        <v>58.71325081200521</v>
       </c>
       <c r="O5" t="n">
-        <v>7.651319973861526</v>
+        <v>7.662457230680325</v>
       </c>
       <c r="P5" t="n">
-        <v>356.6667105877967</v>
+        <v>356.4913552339289</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -24326,28 +24571,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5733619945491629</v>
+        <v>0.5944202811638896</v>
       </c>
       <c r="J6" t="n">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="K6" t="n">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3405632376060687</v>
+        <v>0.3538236587408923</v>
       </c>
       <c r="M6" t="n">
-        <v>4.800986352421607</v>
+        <v>4.868337734797033</v>
       </c>
       <c r="N6" t="n">
-        <v>38.09689479612018</v>
+        <v>39.03991602458667</v>
       </c>
       <c r="O6" t="n">
-        <v>6.17226820513498</v>
+        <v>6.248193020753014</v>
       </c>
       <c r="P6" t="n">
-        <v>337.341554374671</v>
+        <v>337.1234861916012</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -24404,28 +24649,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4600084655760253</v>
+        <v>0.4752815503956202</v>
       </c>
       <c r="J7" t="n">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="K7" t="n">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="L7" t="n">
-        <v>0.227296850418082</v>
+        <v>0.2397911950195821</v>
       </c>
       <c r="M7" t="n">
-        <v>4.773880172708939</v>
+        <v>4.817862997536927</v>
       </c>
       <c r="N7" t="n">
-        <v>43.05338454330048</v>
+        <v>43.32704087248849</v>
       </c>
       <c r="O7" t="n">
-        <v>6.561507794958448</v>
+        <v>6.582327921980831</v>
       </c>
       <c r="P7" t="n">
-        <v>337.4537284090177</v>
+        <v>337.2955605653685</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -24482,28 +24727,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6598964801958931</v>
+        <v>0.6669626113519577</v>
       </c>
       <c r="J8" t="n">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="K8" t="n">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1763397007623707</v>
+        <v>0.1824732836168476</v>
       </c>
       <c r="M8" t="n">
-        <v>7.61591858382589</v>
+        <v>7.5838106992539</v>
       </c>
       <c r="N8" t="n">
-        <v>121.7323603766289</v>
+        <v>120.5766178690548</v>
       </c>
       <c r="O8" t="n">
-        <v>11.03323888876829</v>
+        <v>10.98073849379243</v>
       </c>
       <c r="P8" t="n">
-        <v>331.246068099518</v>
+        <v>331.1729391462433</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -24560,28 +24805,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7443844714815587</v>
+        <v>0.7404461205835369</v>
       </c>
       <c r="J9" t="n">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="K9" t="n">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2064953707043867</v>
+        <v>0.208222847825334</v>
       </c>
       <c r="M9" t="n">
-        <v>7.935535579894929</v>
+        <v>7.860383941817207</v>
       </c>
       <c r="N9" t="n">
-        <v>127.4354156544654</v>
+        <v>126.1301641460943</v>
       </c>
       <c r="O9" t="n">
-        <v>11.28872958549656</v>
+        <v>11.23076863558743</v>
       </c>
       <c r="P9" t="n">
-        <v>328.453887929244</v>
+        <v>328.4946829631186</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -24638,28 +24883,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3633956762974737</v>
+        <v>0.3827324047134065</v>
       </c>
       <c r="J10" t="n">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="K10" t="n">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="L10" t="n">
-        <v>0.07927336542014829</v>
+        <v>0.08796637774583116</v>
       </c>
       <c r="M10" t="n">
-        <v>6.786021701951654</v>
+        <v>6.82327460491657</v>
       </c>
       <c r="N10" t="n">
-        <v>91.94956900420753</v>
+        <v>92.03506470923595</v>
       </c>
       <c r="O10" t="n">
-        <v>9.589033788876099</v>
+        <v>9.59349074681557</v>
       </c>
       <c r="P10" t="n">
-        <v>332.4541622449149</v>
+        <v>332.2541198568896</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -24697,7 +24942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K463"/>
+  <dimension ref="A1:K468"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51063,6 +51308,291 @@
         </is>
       </c>
     </row>
+    <row r="464">
+      <c r="A464" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-24 22:12:29+00:00</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>-41.05100208004656,172.10692283157977</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>-41.050326134572366,172.10684881767673</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>-41.04965820008789,172.1066943491316</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>-41.0489799132552,172.10664369131564</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>-41.04829823381598,172.10662700587903</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>-41.047621402919724,172.10656159930318</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>-41.04694809209675,172.1064608028341</t>
+        </is>
+      </c>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>-41.0462706362714,172.10640152824374</t>
+        </is>
+      </c>
+      <c r="J464" t="inlineStr">
+        <is>
+          <t>-41.04560514140992,172.1062221690814</t>
+        </is>
+      </c>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:18:27+00:00</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>-41.05100291474932,172.10691445573744</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>-41.05032886204433,172.106821449006</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>-41.04965882316918,172.10668809686857</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>-41.0489811594176,172.10663118691795</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>-41.048299432957144,172.1066149734703</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>-41.047622366934156,172.10655192628934</t>
+        </is>
+      </c>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>-41.04694924420657,172.10644924252006</t>
+        </is>
+      </c>
+      <c r="I465" t="inlineStr">
+        <is>
+          <t>-41.04627103598287,172.10639751756372</t>
+        </is>
+      </c>
+      <c r="J465" t="inlineStr">
+        <is>
+          <t>-41.045606587408216,172.10620766000014</t>
+        </is>
+      </c>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:12:05+00:00</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>-41.05100291474932,172.10691445573744</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>-41.05032910892725,172.1068189716693</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>-41.049658458725446,172.10669175385263</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>-41.04898099483021,172.1066328384422</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>-41.04830149030424,172.1065943296308</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>-41.04762256679072,172.10654992090838</t>
+        </is>
+      </c>
+      <c r="H466" t="inlineStr">
+        <is>
+          <t>-41.04694796277821,172.10646210042034</t>
+        </is>
+      </c>
+      <c r="I466" t="inlineStr">
+        <is>
+          <t>-41.04626936659875,172.1064142680506</t>
+        </is>
+      </c>
+      <c r="J466" t="inlineStr">
+        <is>
+          <t>-41.045606587408216,172.10620766000014</t>
+        </is>
+      </c>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:12:23+00:00</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>-41.05101136754979,172.1068296355765</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>-41.05032910892725,172.1068189716693</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>-41.049658458725446,172.10669175385263</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>-41.04898099483021,172.1066328384422</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>-41.048307615298484,172.10653286996427</t>
+        </is>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>-41.047629009206645,172.1064852768573</t>
+        </is>
+      </c>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>-41.04694796277821,172.10646210042034</t>
+        </is>
+      </c>
+      <c r="I467" t="inlineStr">
+        <is>
+          <t>-41.04626936659875,172.1064142680506</t>
+        </is>
+      </c>
+      <c r="J467" t="inlineStr">
+        <is>
+          <t>-41.045606587408216,172.10620766000014</t>
+        </is>
+      </c>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:18:38+00:00</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>-41.05101136754979,172.1068296355765</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>-41.05032910892725,172.1068189716693</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>-41.049658458725446,172.10669175385263</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>-41.04898099483021,172.1066328384422</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>-41.048307615298484,172.10653286996427</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>-41.047629009206645,172.1064852768573</t>
+        </is>
+      </c>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>-41.04694592894858,172.10648250791255</t>
+        </is>
+      </c>
+      <c r="I468" t="inlineStr">
+        <is>
+          <t>-41.04626694481182,172.1064385680513</t>
+        </is>
+      </c>
+      <c r="J468" t="inlineStr">
+        <is>
+          <t>-41.04560133243003,172.10626038812183</t>
+        </is>
+      </c>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
